--- a/docs/sample-output/12-marina/estimate.xlsx
+++ b/docs/sample-output/12-marina/estimate.xlsx
@@ -87,7 +87,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -96,7 +96,7 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
   </si>
   <si>
     <t>Cost by Component   ·   Ashley River Marina · Total $21,008,592</t>
